--- a/Excel/英雄酒馆任务记录与文档汇总.xlsx
+++ b/Excel/英雄酒馆任务记录与文档汇总.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
   <si>
     <t/>
   </si>
@@ -109,6 +109,12 @@
   </si>
   <si>
     <t>放一些美术资源说明</t>
+  </si>
+  <si>
+    <t>文案规则</t>
+  </si>
+  <si>
+    <t>文案表格使用指南</t>
   </si>
   <si>
     <r>
@@ -495,6 +501,70 @@
         <u/>
       </rPr>
       <t>美术角色资源说明</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <color rgb="FF000000"/>
+        <sz val="10"/>
+        <u val="none"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <color rgb="FF175CEB"/>
+        <sz val="10"/>
+        <u/>
+      </rPr>
+      <t>英雄酒馆_文案系统</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <color rgb="FF175CEB"/>
+        <sz val="10"/>
+        <u/>
+      </rPr>
+      <t>英雄酒馆_文案系统</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <color rgb="FF175CEB"/>
+        <sz val="10"/>
+        <u/>
+      </rPr>
+      <t>英雄酒馆_纯文案阅读版</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <color rgb="FF175CEB"/>
+        <sz val="10"/>
+        <u/>
+      </rPr>
+      <t>Dialogue</t>
     </r>
   </si>
 </sst>
@@ -835,7 +905,7 @@
   <sheetPr codeName="001">
     <tabColor/>
   </sheetPr>
-  <dimension ref="E12"/>
+  <dimension ref="F13"/>
   <sheetFormatPr baseColWidth="13" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="21.7539" customWidth="1"/>
@@ -850,10 +920,10 @@
         <v>1</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -861,31 +931,31 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E2" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="F2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G2" t="s">
+        <v>62</v>
+      </c>
+      <c r="H2" t="s">
+        <v>39</v>
+      </c>
+      <c r="I2" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="F2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G2" t="s">
-        <v>36</v>
-      </c>
-      <c r="H2" t="s">
-        <v>37</v>
-      </c>
-      <c r="I2" s="9" t="s">
-        <v>51</v>
-      </c>
       <c r="J2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="9:11" s="10" customFormat="1">
@@ -926,7 +996,7 @@
         <v>11</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -937,13 +1007,13 @@
         <v>12</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>13</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -974,7 +1044,7 @@
         <v>13</v>
       </c>
       <c r="E8" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -991,7 +1061,7 @@
         <v>20</v>
       </c>
       <c r="E9" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1008,7 +1078,7 @@
         <v>11</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1025,7 +1095,7 @@
         <v>13</v>
       </c>
       <c r="E11" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -1042,7 +1112,27 @@
         <v>13</v>
       </c>
       <c r="E12" t="s">
-        <v>56</v>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13">
+        <v>9</v>
+      </c>
+      <c r="B13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="F13" t="s">
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -1066,6 +1156,8 @@
     <hyperlink ref="E10" r:id="rId15"/>
     <hyperlink ref="E11" r:id="rId16"/>
     <hyperlink ref="E12" r:id="rId17"/>
+    <hyperlink ref="E13" r:id="rId18"/>
+    <hyperlink ref="F13" r:id="rId19"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -1080,37 +1172,37 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/英雄酒馆任务记录与文档汇总.xlsx
+++ b/Excel/英雄酒馆任务记录与文档汇总.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
   <si>
     <t/>
   </si>
@@ -115,6 +115,15 @@
   </si>
   <si>
     <t>文案表格使用指南</t>
+  </si>
+  <si>
+    <t>怪物刷新规则、地图场景说明</t>
+  </si>
+  <si>
+    <t>怪物刷新规则、地图场景说明、.......</t>
+  </si>
+  <si>
+    <t>怪物刷新规则、地图场景说明、xxx</t>
   </si>
   <si>
     <r>
@@ -920,10 +929,10 @@
         <v>1</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -931,31 +940,31 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="H2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="J2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="9:11" s="10" customFormat="1">
@@ -996,7 +1005,7 @@
         <v>11</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1007,13 +1016,13 @@
         <v>12</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>13</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1044,7 +1053,7 @@
         <v>13</v>
       </c>
       <c r="E8" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1061,7 +1070,7 @@
         <v>20</v>
       </c>
       <c r="E9" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1078,7 +1087,7 @@
         <v>11</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1089,13 +1098,13 @@
         <v>23</v>
       </c>
       <c r="C11" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>13</v>
       </c>
       <c r="E11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -1112,7 +1121,7 @@
         <v>13</v>
       </c>
       <c r="E12" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1129,10 +1138,10 @@
         <v>13</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F13" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -1172,37 +1181,37 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/英雄酒馆任务记录与文档汇总.xlsx
+++ b/Excel/英雄酒馆任务记录与文档汇总.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="69">
   <si>
     <t/>
   </si>
@@ -124,6 +124,9 @@
   </si>
   <si>
     <t>怪物刷新规则、地图场景说明、xxx</t>
+  </si>
+  <si>
+    <t>仓库系统</t>
   </si>
   <si>
     <r>
@@ -574,6 +577,44 @@
         <u/>
       </rPr>
       <t>Dialogue</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <color rgb="FF000000"/>
+        <sz val="10"/>
+        <u val="none"/>
+      </rPr>
+      <t xml:space="preserve">【腾讯文档】英雄酒馆-悬赏系统需求案
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <color rgb="FF175CEB"/>
+        <sz val="10"/>
+        <u/>
+      </rPr>
+      <t>英雄酒馆-悬赏系统需求案</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <color rgb="FF175CEB"/>
+        <sz val="10"/>
+        <u/>
+      </rPr>
+      <t>英雄酒馆-悬赏系统需求案</t>
     </r>
   </si>
 </sst>
@@ -914,7 +955,7 @@
   <sheetPr codeName="001">
     <tabColor/>
   </sheetPr>
-  <dimension ref="F13"/>
+  <dimension ref="D14"/>
   <sheetFormatPr baseColWidth="13" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="21.7539" customWidth="1"/>
@@ -929,10 +970,10 @@
         <v>1</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -940,31 +981,31 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E2" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="F2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2" t="s">
+        <v>66</v>
+      </c>
+      <c r="H2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="J2" t="s">
         <v>58</v>
-      </c>
-      <c r="F2" t="s">
-        <v>40</v>
-      </c>
-      <c r="G2" t="s">
-        <v>65</v>
-      </c>
-      <c r="H2" t="s">
-        <v>42</v>
-      </c>
-      <c r="I2" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="J2" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="3" spans="9:11" s="10" customFormat="1">
@@ -1005,7 +1046,7 @@
         <v>11</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1016,16 +1057,16 @@
         <v>12</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>13</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7">
         <v>3</v>
       </c>
@@ -1037,6 +1078,9 @@
       </c>
       <c r="D7" t="s">
         <v>11</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1053,7 +1097,7 @@
         <v>13</v>
       </c>
       <c r="E8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1070,7 +1114,7 @@
         <v>20</v>
       </c>
       <c r="E9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1087,7 +1131,7 @@
         <v>11</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1104,7 +1148,7 @@
         <v>13</v>
       </c>
       <c r="E11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -1121,7 +1165,7 @@
         <v>13</v>
       </c>
       <c r="E12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1138,10 +1182,21 @@
         <v>13</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F13" t="s">
-        <v>64</v>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14">
+        <v>10</v>
+      </c>
+      <c r="B14" t="s">
+        <v>34</v>
+      </c>
+      <c r="D14" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1160,13 +1215,14 @@
     <hyperlink ref="E5" r:id="rId11"/>
     <hyperlink ref="C6" r:id="rId12"/>
     <hyperlink ref="E6" r:id="rId1"/>
-    <hyperlink ref="E8" r:id="rId13"/>
-    <hyperlink ref="E9" r:id="rId14"/>
-    <hyperlink ref="E10" r:id="rId15"/>
-    <hyperlink ref="E11" r:id="rId16"/>
-    <hyperlink ref="E12" r:id="rId17"/>
-    <hyperlink ref="E13" r:id="rId18"/>
-    <hyperlink ref="F13" r:id="rId19"/>
+    <hyperlink ref="E7" r:id="rId13"/>
+    <hyperlink ref="E8" r:id="rId14"/>
+    <hyperlink ref="E9" r:id="rId15"/>
+    <hyperlink ref="E10" r:id="rId16"/>
+    <hyperlink ref="E11" r:id="rId17"/>
+    <hyperlink ref="E12" r:id="rId18"/>
+    <hyperlink ref="E13" r:id="rId19"/>
+    <hyperlink ref="F13" r:id="rId20"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -1181,37 +1237,37 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
